--- a/Result/profitability/3227.xlsx
+++ b/Result/profitability/3227.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.89</v>
       </c>
       <c r="M2" t="n">
-        <v>3.135</v>
+        <v>3.155</v>
       </c>
       <c r="N2" t="n">
-        <v>59.85125</v>
+        <v>59.28375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>3.39</v>
       </c>
       <c r="M3" t="n">
-        <v>3.14625</v>
+        <v>3.0975</v>
       </c>
       <c r="N3" t="n">
-        <v>58.215</v>
+        <v>57.55</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>3.04</v>
       </c>
       <c r="M4" t="n">
-        <v>3.045</v>
+        <v>3.01</v>
       </c>
       <c r="N4" t="n">
-        <v>56.18625</v>
+        <v>55.705</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.83375</v>
+        <v>2.9525</v>
       </c>
       <c r="N5" t="n">
-        <v>54.2075</v>
+        <v>53.67875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>2.69</v>
+        <v>2.74625</v>
       </c>
       <c r="N6" t="n">
-        <v>52.60125</v>
+        <v>52.46625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>2.485</v>
+        <v>2.52625</v>
       </c>
       <c r="N7" t="n">
-        <v>50.975</v>
+        <v>50.94</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.28</v>
       </c>
       <c r="M8" t="n">
-        <v>2.37875</v>
+        <v>2.48</v>
       </c>
       <c r="N8" t="n">
-        <v>49.62</v>
+        <v>49.46124999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>2.27125</v>
       </c>
       <c r="N9" t="n">
-        <v>47.56375000000001</v>
+        <v>47.56375</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>1.81125</v>
       </c>
       <c r="N12" t="n">
-        <v>44.5875</v>
+        <v>44.58750000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2538</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1061</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1477</v>
+      </c>
+      <c r="F75" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="G75" t="n">
+        <v>481</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>112</v>
+      </c>
+      <c r="J75" t="n">
+        <v>593</v>
+      </c>
+      <c r="K75" t="n">
+        <v>510</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.20625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>60.78125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3056603773584905</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.269999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02135171486213849</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9500000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3784860557768925</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.229999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06774503523382447</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
